--- a/data/data_target.xlsx
+++ b/data/data_target.xlsx
@@ -882,7 +882,7 @@
         <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -905,7 +905,7 @@
         <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -1135,7 +1135,7 @@
         <v>33</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -1227,7 +1227,7 @@
         <v>37</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
@@ -1273,7 +1273,7 @@
         <v>39</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -1549,7 +1549,7 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -1756,7 +1756,7 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -1802,7 +1802,7 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>81</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -2239,7 +2239,7 @@
         <v>82</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -2285,7 +2285,7 @@
         <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
@@ -2354,7 +2354,7 @@
         <v>87</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
         <v>1</v>
@@ -2377,7 +2377,7 @@
         <v>88</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
@@ -2400,7 +2400,7 @@
         <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
@@ -2469,7 +2469,7 @@
         <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
@@ -3090,7 +3090,7 @@
         <v>119</v>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         <v>120</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>123</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -3688,7 +3688,7 @@
         <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>152</v>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
         <v>1</v>
@@ -3872,7 +3872,7 @@
         <v>153</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
         <v>1</v>
@@ -3987,7 +3987,7 @@
         <v>158</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
@@ -4033,7 +4033,7 @@
         <v>160</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D157" t="n">
         <v>1</v>
@@ -4079,7 +4079,7 @@
         <v>162</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D159" t="n">
         <v>1</v>
@@ -4516,7 +4516,7 @@
         <v>181</v>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D178" t="n">
         <v>1</v>
@@ -4539,7 +4539,7 @@
         <v>182</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         <v>188</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D185" t="n">
         <v>1</v>
@@ -5045,7 +5045,7 @@
         <v>204</v>
       </c>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D201" t="n">
         <v>1</v>
@@ -5183,7 +5183,7 @@
         <v>210</v>
       </c>
       <c r="C207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D207" t="n">
         <v>1</v>
@@ -5436,7 +5436,7 @@
         <v>221</v>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
         <v>1</v>
@@ -5574,7 +5574,7 @@
         <v>227</v>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D224" t="n">
         <v>1</v>
@@ -5689,7 +5689,7 @@
         <v>232</v>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -5919,7 +5919,7 @@
         <v>242</v>
       </c>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -6034,7 +6034,7 @@
         <v>247</v>
       </c>
       <c r="C244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>256</v>
       </c>
       <c r="C253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D253" t="n">
         <v>0</v>
@@ -6333,7 +6333,7 @@
         <v>260</v>
       </c>
       <c r="C257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D257" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>268</v>
       </c>
       <c r="C265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D265" t="n">
         <v>1</v>
@@ -6701,7 +6701,7 @@
         <v>276</v>
       </c>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -6793,7 +6793,7 @@
         <v>281</v>
       </c>
       <c r="C277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D277" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
         <v>287</v>
       </c>
       <c r="C283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D283" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
         <v>318</v>
       </c>
       <c r="C314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D314" t="n">
         <v>1</v>
@@ -8104,7 +8104,7 @@
         <v>338</v>
       </c>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D334" t="n">
         <v>0</v>
@@ -8817,7 +8817,7 @@
         <v>369</v>
       </c>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D365" t="n">
         <v>1</v>
@@ -9070,7 +9070,7 @@
         <v>380</v>
       </c>
       <c r="C376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D376" t="n">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>387</v>
       </c>
       <c r="C383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D383" t="n">
         <v>0</v>
